--- a/Kachi_Gun/Table/Boss_Dungeon.xlsx
+++ b/Kachi_Gun/Table/Boss_Dungeon.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Reward_Ad_x3_Gems</t>
+          <t>Reward_Ad_x2_Gems</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -645,13 +645,13 @@
         <v>0</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
@@ -705,16 +705,16 @@
         <v>2.3</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>110</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
@@ -768,16 +768,16 @@
         <v>2.3</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>180</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
@@ -831,16 +831,16 @@
         <v>2.3</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>240</v>
+        <v>92</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>260</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
@@ -894,16 +894,16 @@
         <v>2.3</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>270</v>
+        <v>104</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>350</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
@@ -957,16 +957,16 @@
         <v>2.3</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>300</v>
+        <v>116</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>450</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -1020,16 +1020,16 @@
         <v>2.3</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>330</v>
+        <v>126</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>560</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
@@ -1083,16 +1083,16 @@
         <v>2.3</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>360</v>
+        <v>138</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>680</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -1146,16 +1146,16 @@
         <v>2.3</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>390</v>
+        <v>150</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>810</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
@@ -1209,16 +1209,16 @@
         <v>2.3</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>420</v>
+        <v>162</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>950</v>
+        <v>548</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
@@ -1272,16 +1272,16 @@
         <v>2.3</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>450</v>
+        <v>174</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>1100</v>
+        <v>635</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
@@ -1335,16 +1335,16 @@
         <v>2.3</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>160</v>
+        <v>92</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>480</v>
+        <v>184</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>1260</v>
+        <v>727</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
@@ -1398,16 +1398,16 @@
         <v>2.3</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>170</v>
+        <v>98</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>510</v>
+        <v>196</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>1430</v>
+        <v>825</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
@@ -1461,16 +1461,16 @@
         <v>2.3</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>540</v>
+        <v>208</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>1610</v>
+        <v>929</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
@@ -1524,16 +1524,16 @@
         <v>2.3</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>570</v>
+        <v>220</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>1800</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
@@ -1587,16 +1587,16 @@
         <v>2.3</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>200</v>
+        <v>115</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>600</v>
+        <v>230</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>2000</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
@@ -1650,16 +1650,16 @@
         <v>2.3</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>210</v>
+        <v>121</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>630</v>
+        <v>242</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>2210</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
@@ -1713,16 +1713,16 @@
         <v>2.3</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>220</v>
+        <v>127</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>660</v>
+        <v>254</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>2430</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
@@ -1776,16 +1776,16 @@
         <v>2.3</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>230</v>
+        <v>133</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>690</v>
+        <v>266</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>2660</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
@@ -1839,16 +1839,16 @@
         <v>2.3</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>240</v>
+        <v>138</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>720</v>
+        <v>276</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>2900</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
@@ -1902,16 +1902,16 @@
         <v>2.3</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>250</v>
+        <v>144</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>750</v>
+        <v>288</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>3150</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -1965,16 +1965,16 @@
         <v>2.3</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>780</v>
+        <v>300</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>3410</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
@@ -2028,16 +2028,16 @@
         <v>2.3</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>270</v>
+        <v>156</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>810</v>
+        <v>312</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>3680</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -2091,16 +2091,16 @@
         <v>2.3</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>280</v>
+        <v>162</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>840</v>
+        <v>324</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>3960</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
@@ -2154,16 +2154,16 @@
         <v>2.3</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>290</v>
+        <v>167</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>870</v>
+        <v>334</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>4250</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
@@ -2217,16 +2217,16 @@
         <v>2.3</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>300</v>
+        <v>173</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>900</v>
+        <v>346</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>4550</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
@@ -2280,16 +2280,16 @@
         <v>2.3</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>310</v>
+        <v>179</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>930</v>
+        <v>358</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>4860</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
@@ -2343,16 +2343,16 @@
         <v>2.3</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>320</v>
+        <v>185</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>960</v>
+        <v>370</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>5180</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
@@ -2406,16 +2406,16 @@
         <v>2.3</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>330</v>
+        <v>190</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>990</v>
+        <v>380</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>5510</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
@@ -2469,16 +2469,16 @@
         <v>2.3</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>340</v>
+        <v>196</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>1020</v>
+        <v>392</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>5850</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
@@ -2532,16 +2532,16 @@
         <v>2.3</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>350</v>
+        <v>202</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>1050</v>
+        <v>404</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>6200</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
@@ -2595,16 +2595,16 @@
         <v>2.3</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>360</v>
+        <v>208</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>1080</v>
+        <v>416</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>6560</v>
+        <v>3785</v>
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
@@ -2658,16 +2658,16 @@
         <v>2.3</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>370</v>
+        <v>213</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>1110</v>
+        <v>426</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>6930</v>
+        <v>3998</v>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
@@ -2721,16 +2721,16 @@
         <v>2.3</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>380</v>
+        <v>219</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>1140</v>
+        <v>438</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>7310</v>
+        <v>4217</v>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
@@ -2784,16 +2784,16 @@
         <v>2.3</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>390</v>
+        <v>225</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>1170</v>
+        <v>450</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>7700</v>
+        <v>4442</v>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
@@ -2847,16 +2847,16 @@
         <v>2.3</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>400</v>
+        <v>231</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>1200</v>
+        <v>462</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>8100</v>
+        <v>4673</v>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
@@ -2910,16 +2910,16 @@
         <v>2.3</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>410</v>
+        <v>237</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1230</v>
+        <v>474</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>8510</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
@@ -2973,16 +2973,16 @@
         <v>2.3</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>420</v>
+        <v>242</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>1260</v>
+        <v>484</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>8930</v>
+        <v>5152</v>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
@@ -3036,16 +3036,16 @@
         <v>2.3</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>430</v>
+        <v>248</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>1290</v>
+        <v>496</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>9360</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
@@ -3099,16 +3099,16 @@
         <v>2.3</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>440</v>
+        <v>254</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>1320</v>
+        <v>508</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>9800</v>
+        <v>5654</v>
       </c>
     </row>
     <row r="42" ht="19" customHeight="1">
@@ -3162,16 +3162,16 @@
         <v>2.3</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>450</v>
+        <v>260</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>1350</v>
+        <v>520</v>
       </c>
       <c r="Q42" s="6" t="n">
-        <v>10250</v>
+        <v>5914</v>
       </c>
     </row>
     <row r="43" ht="19" customHeight="1">
@@ -3225,16 +3225,16 @@
         <v>2.3</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>460</v>
+        <v>265</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>1380</v>
+        <v>530</v>
       </c>
       <c r="Q43" s="6" t="n">
-        <v>10710</v>
+        <v>6179</v>
       </c>
     </row>
     <row r="44" ht="19" customHeight="1">
@@ -3288,16 +3288,16 @@
         <v>2.3</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>470</v>
+        <v>271</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>1410</v>
+        <v>542</v>
       </c>
       <c r="Q44" s="6" t="n">
-        <v>11180</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="45" ht="19" customHeight="1">
@@ -3351,16 +3351,16 @@
         <v>2.3</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>480</v>
+        <v>277</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>1440</v>
+        <v>554</v>
       </c>
       <c r="Q45" s="6" t="n">
-        <v>11660</v>
+        <v>6727</v>
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
@@ -3414,16 +3414,16 @@
         <v>2.3</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>490</v>
+        <v>283</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>1470</v>
+        <v>566</v>
       </c>
       <c r="Q46" s="6" t="n">
-        <v>12150</v>
+        <v>7010</v>
       </c>
     </row>
     <row r="47" ht="19" customHeight="1">
@@ -3477,16 +3477,16 @@
         <v>2.3</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>500</v>
+        <v>288</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>1500</v>
+        <v>576</v>
       </c>
       <c r="Q47" s="6" t="n">
-        <v>12650</v>
+        <v>7298</v>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
@@ -3540,16 +3540,16 @@
         <v>2.3</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>510</v>
+        <v>294</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>1530</v>
+        <v>588</v>
       </c>
       <c r="Q48" s="6" t="n">
-        <v>13160</v>
+        <v>7592</v>
       </c>
     </row>
     <row r="49" ht="19" customHeight="1">
@@ -3603,16 +3603,16 @@
         <v>2.3</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>520</v>
+        <v>300</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>1560</v>
+        <v>600</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>13680</v>
+        <v>7892</v>
       </c>
     </row>
     <row r="50" ht="19" customHeight="1">
@@ -3666,16 +3666,16 @@
         <v>2.3</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>530</v>
+        <v>306</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>1590</v>
+        <v>612</v>
       </c>
       <c r="Q50" s="6" t="n">
-        <v>14210</v>
+        <v>8198</v>
       </c>
     </row>
     <row r="51" ht="19" customHeight="1">
@@ -3729,16 +3729,16 @@
         <v>2.3</v>
       </c>
       <c r="N51" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>540</v>
+        <v>312</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>1620</v>
+        <v>624</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>14750</v>
+        <v>8510</v>
       </c>
     </row>
     <row r="52" ht="19" customHeight="1">
@@ -3792,16 +3792,16 @@
         <v>2.3</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>555</v>
+        <v>320</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>1665</v>
+        <v>640</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>15305</v>
+        <v>8830</v>
       </c>
     </row>
     <row r="53" ht="19" customHeight="1">
@@ -3855,16 +3855,16 @@
         <v>2.3</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>570</v>
+        <v>329</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>1710</v>
+        <v>658</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>15875</v>
+        <v>9159</v>
       </c>
     </row>
     <row r="54" ht="19" customHeight="1">
@@ -3918,16 +3918,16 @@
         <v>2.3</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>585</v>
+        <v>338</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>1755</v>
+        <v>676</v>
       </c>
       <c r="Q54" s="6" t="n">
-        <v>16460</v>
+        <v>9497</v>
       </c>
     </row>
     <row r="55" ht="19" customHeight="1">
@@ -3981,16 +3981,16 @@
         <v>2.3</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>600</v>
+        <v>346</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>1800</v>
+        <v>692</v>
       </c>
       <c r="Q55" s="6" t="n">
-        <v>17060</v>
+        <v>9843</v>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
@@ -4044,16 +4044,16 @@
         <v>2.3</v>
       </c>
       <c r="N56" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>615</v>
+        <v>355</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>1845</v>
+        <v>710</v>
       </c>
       <c r="Q56" s="6" t="n">
-        <v>17675</v>
+        <v>10198</v>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
@@ -4107,16 +4107,16 @@
         <v>2.3</v>
       </c>
       <c r="N57" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>630</v>
+        <v>364</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>1890</v>
+        <v>728</v>
       </c>
       <c r="Q57" s="6" t="n">
-        <v>18305</v>
+        <v>10562</v>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
@@ -4170,16 +4170,16 @@
         <v>2.3</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>645</v>
+        <v>372</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>1935</v>
+        <v>744</v>
       </c>
       <c r="Q58" s="6" t="n">
-        <v>18950</v>
+        <v>10934</v>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
@@ -4233,16 +4233,16 @@
         <v>2.3</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>660</v>
+        <v>381</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>1980</v>
+        <v>762</v>
       </c>
       <c r="Q59" s="6" t="n">
-        <v>19610</v>
+        <v>11315</v>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
@@ -4296,16 +4296,16 @@
         <v>2.3</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>675</v>
+        <v>389</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>2025</v>
+        <v>778</v>
       </c>
       <c r="Q60" s="6" t="n">
-        <v>20285</v>
+        <v>11704</v>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
@@ -4359,16 +4359,16 @@
         <v>2.3</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>690</v>
+        <v>398</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>2070</v>
+        <v>796</v>
       </c>
       <c r="Q61" s="6" t="n">
-        <v>20975</v>
+        <v>12102</v>
       </c>
     </row>
     <row r="62" ht="19" customHeight="1">
@@ -4422,16 +4422,16 @@
         <v>2.3</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>705</v>
+        <v>407</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>2115</v>
+        <v>814</v>
       </c>
       <c r="Q62" s="6" t="n">
-        <v>21680</v>
+        <v>12509</v>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
@@ -4485,16 +4485,16 @@
         <v>2.3</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>720</v>
+        <v>415</v>
       </c>
       <c r="P63" s="6" t="n">
-        <v>2160</v>
+        <v>830</v>
       </c>
       <c r="Q63" s="6" t="n">
-        <v>22400</v>
+        <v>12924</v>
       </c>
     </row>
     <row r="64" ht="19" customHeight="1">
@@ -4548,16 +4548,16 @@
         <v>2.3</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>735</v>
+        <v>424</v>
       </c>
       <c r="P64" s="6" t="n">
-        <v>2205</v>
+        <v>848</v>
       </c>
       <c r="Q64" s="6" t="n">
-        <v>23135</v>
+        <v>13348</v>
       </c>
     </row>
     <row r="65" ht="19" customHeight="1">
@@ -4611,16 +4611,16 @@
         <v>2.3</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>750</v>
+        <v>433</v>
       </c>
       <c r="P65" s="6" t="n">
-        <v>2250</v>
+        <v>866</v>
       </c>
       <c r="Q65" s="6" t="n">
-        <v>23885</v>
+        <v>13781</v>
       </c>
     </row>
     <row r="66" ht="19" customHeight="1">
@@ -4674,16 +4674,16 @@
         <v>2.3</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>765</v>
+        <v>441</v>
       </c>
       <c r="P66" s="6" t="n">
-        <v>2295</v>
+        <v>882</v>
       </c>
       <c r="Q66" s="6" t="n">
-        <v>24650</v>
+        <v>14222</v>
       </c>
     </row>
     <row r="67" ht="19" customHeight="1">
@@ -4737,16 +4737,16 @@
         <v>2.3</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>780</v>
+        <v>450</v>
       </c>
       <c r="P67" s="6" t="n">
-        <v>2340</v>
+        <v>900</v>
       </c>
       <c r="Q67" s="6" t="n">
-        <v>25430</v>
+        <v>14672</v>
       </c>
     </row>
     <row r="68" ht="19" customHeight="1">
@@ -4800,16 +4800,16 @@
         <v>2.3</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>795</v>
+        <v>459</v>
       </c>
       <c r="P68" s="6" t="n">
-        <v>2385</v>
+        <v>918</v>
       </c>
       <c r="Q68" s="6" t="n">
-        <v>26225</v>
+        <v>15131</v>
       </c>
     </row>
     <row r="69" ht="19" customHeight="1">
@@ -4863,16 +4863,16 @@
         <v>2.3</v>
       </c>
       <c r="N69" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>810</v>
+        <v>467</v>
       </c>
       <c r="P69" s="6" t="n">
-        <v>2430</v>
+        <v>934</v>
       </c>
       <c r="Q69" s="6" t="n">
-        <v>27035</v>
+        <v>15598</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1">
@@ -4926,16 +4926,16 @@
         <v>2.3</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>825</v>
+        <v>476</v>
       </c>
       <c r="P70" s="6" t="n">
-        <v>2475</v>
+        <v>952</v>
       </c>
       <c r="Q70" s="6" t="n">
-        <v>27860</v>
+        <v>16074</v>
       </c>
     </row>
     <row r="71" ht="19" customHeight="1">
@@ -4989,16 +4989,16 @@
         <v>2.3</v>
       </c>
       <c r="N71" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>840</v>
+        <v>485</v>
       </c>
       <c r="P71" s="6" t="n">
-        <v>2520</v>
+        <v>970</v>
       </c>
       <c r="Q71" s="6" t="n">
-        <v>28700</v>
+        <v>16559</v>
       </c>
     </row>
     <row r="72" ht="19" customHeight="1">
@@ -5052,16 +5052,16 @@
         <v>2.3</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>855</v>
+        <v>493</v>
       </c>
       <c r="P72" s="6" t="n">
-        <v>2565</v>
+        <v>986</v>
       </c>
       <c r="Q72" s="6" t="n">
-        <v>29555</v>
+        <v>17052</v>
       </c>
     </row>
     <row r="73" ht="19" customHeight="1">
@@ -5115,16 +5115,16 @@
         <v>2.3</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>870</v>
+        <v>502</v>
       </c>
       <c r="P73" s="6" t="n">
-        <v>2610</v>
+        <v>1004</v>
       </c>
       <c r="Q73" s="6" t="n">
-        <v>30425</v>
+        <v>17554</v>
       </c>
     </row>
     <row r="74" ht="19" customHeight="1">
@@ -5178,16 +5178,16 @@
         <v>2.3</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>885</v>
+        <v>511</v>
       </c>
       <c r="P74" s="6" t="n">
-        <v>2655</v>
+        <v>1022</v>
       </c>
       <c r="Q74" s="6" t="n">
-        <v>31310</v>
+        <v>18065</v>
       </c>
     </row>
     <row r="75" ht="19" customHeight="1">
@@ -5241,16 +5241,16 @@
         <v>2.3</v>
       </c>
       <c r="N75" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>900</v>
+        <v>519</v>
       </c>
       <c r="P75" s="6" t="n">
-        <v>2700</v>
+        <v>1038</v>
       </c>
       <c r="Q75" s="6" t="n">
-        <v>32210</v>
+        <v>18584</v>
       </c>
     </row>
     <row r="76" ht="19" customHeight="1">
@@ -5304,16 +5304,16 @@
         <v>2.3</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>915</v>
+        <v>528</v>
       </c>
       <c r="P76" s="6" t="n">
-        <v>2745</v>
+        <v>1056</v>
       </c>
       <c r="Q76" s="6" t="n">
-        <v>33125</v>
+        <v>19112</v>
       </c>
     </row>
     <row r="77" ht="19" customHeight="1">
@@ -5367,16 +5367,16 @@
         <v>2.3</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>930</v>
+        <v>537</v>
       </c>
       <c r="P77" s="6" t="n">
-        <v>2790</v>
+        <v>1074</v>
       </c>
       <c r="Q77" s="6" t="n">
-        <v>34055</v>
+        <v>19649</v>
       </c>
     </row>
     <row r="78" ht="19" customHeight="1">
@@ -5430,16 +5430,16 @@
         <v>2.3</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>945</v>
+        <v>545</v>
       </c>
       <c r="P78" s="6" t="n">
-        <v>2835</v>
+        <v>1090</v>
       </c>
       <c r="Q78" s="6" t="n">
-        <v>35000</v>
+        <v>20194</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1">
@@ -5493,16 +5493,16 @@
         <v>2.3</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>960</v>
+        <v>554</v>
       </c>
       <c r="P79" s="6" t="n">
-        <v>2880</v>
+        <v>1108</v>
       </c>
       <c r="Q79" s="6" t="n">
-        <v>35960</v>
+        <v>20748</v>
       </c>
     </row>
     <row r="80" ht="19" customHeight="1">
@@ -5556,16 +5556,16 @@
         <v>2.3</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>975</v>
+        <v>563</v>
       </c>
       <c r="P80" s="6" t="n">
-        <v>2925</v>
+        <v>1126</v>
       </c>
       <c r="Q80" s="6" t="n">
-        <v>36935</v>
+        <v>21311</v>
       </c>
     </row>
     <row r="81" ht="19" customHeight="1">
@@ -5619,16 +5619,16 @@
         <v>2.3</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>990</v>
+        <v>571</v>
       </c>
       <c r="P81" s="6" t="n">
-        <v>2970</v>
+        <v>1142</v>
       </c>
       <c r="Q81" s="6" t="n">
-        <v>37925</v>
+        <v>21882</v>
       </c>
     </row>
     <row r="82" ht="19" customHeight="1">
@@ -5682,16 +5682,16 @@
         <v>2.3</v>
       </c>
       <c r="N82" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O82" s="6" t="n">
-        <v>1005</v>
+        <v>580</v>
       </c>
       <c r="P82" s="6" t="n">
-        <v>3015</v>
+        <v>1160</v>
       </c>
       <c r="Q82" s="6" t="n">
-        <v>38930</v>
+        <v>22462</v>
       </c>
     </row>
     <row r="83" ht="19" customHeight="1">
@@ -5745,16 +5745,16 @@
         <v>2.3</v>
       </c>
       <c r="N83" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O83" s="6" t="n">
-        <v>1020</v>
+        <v>589</v>
       </c>
       <c r="P83" s="6" t="n">
-        <v>3060</v>
+        <v>1178</v>
       </c>
       <c r="Q83" s="6" t="n">
-        <v>39950</v>
+        <v>23051</v>
       </c>
     </row>
     <row r="84" ht="19" customHeight="1">
@@ -5808,16 +5808,16 @@
         <v>2.3</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O84" s="6" t="n">
-        <v>1035</v>
+        <v>597</v>
       </c>
       <c r="P84" s="6" t="n">
-        <v>3105</v>
+        <v>1194</v>
       </c>
       <c r="Q84" s="6" t="n">
-        <v>40985</v>
+        <v>23648</v>
       </c>
     </row>
     <row r="85" ht="19" customHeight="1">
@@ -5871,16 +5871,16 @@
         <v>2.3</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O85" s="6" t="n">
-        <v>1050</v>
+        <v>606</v>
       </c>
       <c r="P85" s="6" t="n">
-        <v>3150</v>
+        <v>1212</v>
       </c>
       <c r="Q85" s="6" t="n">
-        <v>42035</v>
+        <v>24254</v>
       </c>
     </row>
     <row r="86" ht="19" customHeight="1">
@@ -5934,16 +5934,16 @@
         <v>2.3</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O86" s="6" t="n">
-        <v>1065</v>
+        <v>615</v>
       </c>
       <c r="P86" s="6" t="n">
-        <v>3195</v>
+        <v>1230</v>
       </c>
       <c r="Q86" s="6" t="n">
-        <v>43100</v>
+        <v>24869</v>
       </c>
     </row>
     <row r="87" ht="19" customHeight="1">
@@ -5997,16 +5997,16 @@
         <v>2.3</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O87" s="6" t="n">
-        <v>1080</v>
+        <v>623</v>
       </c>
       <c r="P87" s="6" t="n">
-        <v>3240</v>
+        <v>1246</v>
       </c>
       <c r="Q87" s="6" t="n">
-        <v>44180</v>
+        <v>25492</v>
       </c>
     </row>
     <row r="88" ht="19" customHeight="1">
@@ -6060,16 +6060,16 @@
         <v>2.3</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O88" s="6" t="n">
-        <v>1095</v>
+        <v>632</v>
       </c>
       <c r="P88" s="6" t="n">
-        <v>3285</v>
+        <v>1264</v>
       </c>
       <c r="Q88" s="6" t="n">
-        <v>45275</v>
+        <v>26124</v>
       </c>
     </row>
     <row r="89" ht="19" customHeight="1">
@@ -6123,16 +6123,16 @@
         <v>2.3</v>
       </c>
       <c r="N89" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O89" s="6" t="n">
-        <v>1110</v>
+        <v>640</v>
       </c>
       <c r="P89" s="6" t="n">
-        <v>3330</v>
+        <v>1280</v>
       </c>
       <c r="Q89" s="6" t="n">
-        <v>46385</v>
+        <v>26764</v>
       </c>
     </row>
     <row r="90" ht="19" customHeight="1">
@@ -6186,16 +6186,16 @@
         <v>2.3</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O90" s="6" t="n">
-        <v>1125</v>
+        <v>649</v>
       </c>
       <c r="P90" s="6" t="n">
-        <v>3375</v>
+        <v>1298</v>
       </c>
       <c r="Q90" s="6" t="n">
-        <v>47510</v>
+        <v>27413</v>
       </c>
     </row>
     <row r="91" ht="19" customHeight="1">
@@ -6249,16 +6249,16 @@
         <v>2.3</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O91" s="6" t="n">
-        <v>1140</v>
+        <v>658</v>
       </c>
       <c r="P91" s="6" t="n">
-        <v>3420</v>
+        <v>1316</v>
       </c>
       <c r="Q91" s="6" t="n">
-        <v>48650</v>
+        <v>28071</v>
       </c>
     </row>
     <row r="92" ht="19" customHeight="1">
@@ -6312,16 +6312,16 @@
         <v>2.3</v>
       </c>
       <c r="N92" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O92" s="6" t="n">
-        <v>1155</v>
+        <v>666</v>
       </c>
       <c r="P92" s="6" t="n">
-        <v>3465</v>
+        <v>1332</v>
       </c>
       <c r="Q92" s="6" t="n">
-        <v>49805</v>
+        <v>28737</v>
       </c>
     </row>
     <row r="93" ht="19" customHeight="1">
@@ -6375,16 +6375,16 @@
         <v>2.3</v>
       </c>
       <c r="N93" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O93" s="6" t="n">
-        <v>1170</v>
+        <v>675</v>
       </c>
       <c r="P93" s="6" t="n">
-        <v>3510</v>
+        <v>1350</v>
       </c>
       <c r="Q93" s="6" t="n">
-        <v>50975</v>
+        <v>29412</v>
       </c>
     </row>
     <row r="94" ht="19" customHeight="1">
@@ -6438,16 +6438,16 @@
         <v>2.3</v>
       </c>
       <c r="N94" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O94" s="6" t="n">
-        <v>1185</v>
+        <v>684</v>
       </c>
       <c r="P94" s="6" t="n">
-        <v>3555</v>
+        <v>1368</v>
       </c>
       <c r="Q94" s="6" t="n">
-        <v>52160</v>
+        <v>30096</v>
       </c>
     </row>
     <row r="95" ht="19" customHeight="1">
@@ -6501,16 +6501,16 @@
         <v>2.3</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O95" s="6" t="n">
-        <v>1200</v>
+        <v>692</v>
       </c>
       <c r="P95" s="6" t="n">
-        <v>3600</v>
+        <v>1384</v>
       </c>
       <c r="Q95" s="6" t="n">
-        <v>53360</v>
+        <v>30788</v>
       </c>
     </row>
     <row r="96" ht="19" customHeight="1">
@@ -6564,16 +6564,16 @@
         <v>2.3</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O96" s="6" t="n">
-        <v>1215</v>
+        <v>701</v>
       </c>
       <c r="P96" s="6" t="n">
-        <v>3645</v>
+        <v>1402</v>
       </c>
       <c r="Q96" s="6" t="n">
-        <v>54575</v>
+        <v>31489</v>
       </c>
     </row>
     <row r="97" ht="19" customHeight="1">
@@ -6627,16 +6627,16 @@
         <v>2.3</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O97" s="6" t="n">
-        <v>1230</v>
+        <v>710</v>
       </c>
       <c r="P97" s="6" t="n">
-        <v>3690</v>
+        <v>1420</v>
       </c>
       <c r="Q97" s="6" t="n">
-        <v>55805</v>
+        <v>32199</v>
       </c>
     </row>
     <row r="98" ht="19" customHeight="1">
@@ -6690,16 +6690,16 @@
         <v>2.3</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O98" s="6" t="n">
-        <v>1245</v>
+        <v>718</v>
       </c>
       <c r="P98" s="6" t="n">
-        <v>3735</v>
+        <v>1436</v>
       </c>
       <c r="Q98" s="6" t="n">
-        <v>57050</v>
+        <v>32917</v>
       </c>
     </row>
     <row r="99" ht="19" customHeight="1">
@@ -6753,16 +6753,16 @@
         <v>2.3</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O99" s="6" t="n">
-        <v>1260</v>
+        <v>727</v>
       </c>
       <c r="P99" s="6" t="n">
-        <v>3780</v>
+        <v>1454</v>
       </c>
       <c r="Q99" s="6" t="n">
-        <v>58310</v>
+        <v>33644</v>
       </c>
     </row>
     <row r="100" ht="19" customHeight="1">
@@ -6816,16 +6816,16 @@
         <v>2.3</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O100" s="6" t="n">
-        <v>1275</v>
+        <v>736</v>
       </c>
       <c r="P100" s="6" t="n">
-        <v>3825</v>
+        <v>1472</v>
       </c>
       <c r="Q100" s="6" t="n">
-        <v>59585</v>
+        <v>34380</v>
       </c>
     </row>
     <row r="101" ht="19" customHeight="1">
@@ -6879,16 +6879,16 @@
         <v>2.3</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O101" s="6" t="n">
-        <v>1290</v>
+        <v>744</v>
       </c>
       <c r="P101" s="6" t="n">
-        <v>3870</v>
+        <v>1488</v>
       </c>
       <c r="Q101" s="6" t="n">
-        <v>60875</v>
+        <v>35124</v>
       </c>
     </row>
     <row r="102" ht="19" customHeight="1">
@@ -6942,16 +6942,16 @@
         <v>2.3</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O102" s="6" t="n">
-        <v>1310</v>
+        <v>756</v>
       </c>
       <c r="P102" s="6" t="n">
-        <v>3930</v>
+        <v>1512</v>
       </c>
       <c r="Q102" s="6" t="n">
-        <v>62185</v>
+        <v>35880</v>
       </c>
     </row>
     <row r="103" ht="19" customHeight="1">
@@ -7005,16 +7005,16 @@
         <v>2.3</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O103" s="6" t="n">
-        <v>1330</v>
+        <v>767</v>
       </c>
       <c r="P103" s="6" t="n">
-        <v>3990</v>
+        <v>1534</v>
       </c>
       <c r="Q103" s="6" t="n">
-        <v>63515</v>
+        <v>36647</v>
       </c>
     </row>
     <row r="104" ht="19" customHeight="1">
@@ -7068,16 +7068,16 @@
         <v>2.3</v>
       </c>
       <c r="N104" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O104" s="6" t="n">
-        <v>1350</v>
+        <v>779</v>
       </c>
       <c r="P104" s="6" t="n">
-        <v>4050</v>
+        <v>1558</v>
       </c>
       <c r="Q104" s="6" t="n">
-        <v>64865</v>
+        <v>37426</v>
       </c>
     </row>
     <row r="105" ht="19" customHeight="1">
@@ -7131,16 +7131,16 @@
         <v>2.3</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O105" s="6" t="n">
-        <v>1370</v>
+        <v>790</v>
       </c>
       <c r="P105" s="6" t="n">
-        <v>4110</v>
+        <v>1580</v>
       </c>
       <c r="Q105" s="6" t="n">
-        <v>66235</v>
+        <v>38216</v>
       </c>
     </row>
     <row r="106" ht="19" customHeight="1">
@@ -7194,16 +7194,16 @@
         <v>2.3</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O106" s="6" t="n">
-        <v>1390</v>
+        <v>802</v>
       </c>
       <c r="P106" s="6" t="n">
-        <v>4170</v>
+        <v>1604</v>
       </c>
       <c r="Q106" s="6" t="n">
-        <v>67625</v>
+        <v>39018</v>
       </c>
     </row>
     <row r="107" ht="19" customHeight="1">
@@ -7257,16 +7257,16 @@
         <v>2.3</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O107" s="6" t="n">
-        <v>1410</v>
+        <v>814</v>
       </c>
       <c r="P107" s="6" t="n">
-        <v>4230</v>
+        <v>1628</v>
       </c>
       <c r="Q107" s="6" t="n">
-        <v>69035</v>
+        <v>39832</v>
       </c>
     </row>
     <row r="108" ht="19" customHeight="1">
@@ -7320,16 +7320,16 @@
         <v>2.3</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O108" s="6" t="n">
-        <v>1430</v>
+        <v>825</v>
       </c>
       <c r="P108" s="6" t="n">
-        <v>4290</v>
+        <v>1650</v>
       </c>
       <c r="Q108" s="6" t="n">
-        <v>70465</v>
+        <v>40657</v>
       </c>
     </row>
     <row r="109" ht="19" customHeight="1">
@@ -7383,16 +7383,16 @@
         <v>2.3</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O109" s="6" t="n">
-        <v>1450</v>
+        <v>837</v>
       </c>
       <c r="P109" s="6" t="n">
-        <v>4350</v>
+        <v>1674</v>
       </c>
       <c r="Q109" s="6" t="n">
-        <v>71915</v>
+        <v>41494</v>
       </c>
     </row>
     <row r="110" ht="19" customHeight="1">
@@ -7446,16 +7446,16 @@
         <v>2.3</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O110" s="6" t="n">
-        <v>1470</v>
+        <v>848</v>
       </c>
       <c r="P110" s="6" t="n">
-        <v>4410</v>
+        <v>1696</v>
       </c>
       <c r="Q110" s="6" t="n">
-        <v>73385</v>
+        <v>42342</v>
       </c>
     </row>
     <row r="111" ht="19" customHeight="1">
@@ -7509,16 +7509,16 @@
         <v>2.3</v>
       </c>
       <c r="N111" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O111" s="6" t="n">
-        <v>1490</v>
+        <v>860</v>
       </c>
       <c r="P111" s="6" t="n">
-        <v>4470</v>
+        <v>1720</v>
       </c>
       <c r="Q111" s="6" t="n">
-        <v>74875</v>
+        <v>43202</v>
       </c>
     </row>
     <row r="112" ht="19" customHeight="1">
@@ -7572,16 +7572,16 @@
         <v>2.3</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O112" s="6" t="n">
-        <v>1510</v>
+        <v>871</v>
       </c>
       <c r="P112" s="6" t="n">
-        <v>4530</v>
+        <v>1742</v>
       </c>
       <c r="Q112" s="6" t="n">
-        <v>76385</v>
+        <v>44073</v>
       </c>
     </row>
     <row r="113" ht="19" customHeight="1">
@@ -7635,16 +7635,16 @@
         <v>2.3</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O113" s="6" t="n">
-        <v>1530</v>
+        <v>883</v>
       </c>
       <c r="P113" s="6" t="n">
-        <v>4590</v>
+        <v>1766</v>
       </c>
       <c r="Q113" s="6" t="n">
-        <v>77915</v>
+        <v>44956</v>
       </c>
     </row>
     <row r="114" ht="19" customHeight="1">
@@ -7698,16 +7698,16 @@
         <v>2.3</v>
       </c>
       <c r="N114" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O114" s="6" t="n">
-        <v>1550</v>
+        <v>894</v>
       </c>
       <c r="P114" s="6" t="n">
-        <v>4650</v>
+        <v>1788</v>
       </c>
       <c r="Q114" s="6" t="n">
-        <v>79465</v>
+        <v>45850</v>
       </c>
     </row>
     <row r="115" ht="19" customHeight="1">
@@ -7761,16 +7761,16 @@
         <v>2.3</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O115" s="6" t="n">
-        <v>1570</v>
+        <v>906</v>
       </c>
       <c r="P115" s="6" t="n">
-        <v>4710</v>
+        <v>1812</v>
       </c>
       <c r="Q115" s="6" t="n">
-        <v>81035</v>
+        <v>46756</v>
       </c>
     </row>
     <row r="116" ht="19" customHeight="1">
@@ -7824,16 +7824,16 @@
         <v>2.3</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O116" s="6" t="n">
-        <v>1590</v>
+        <v>917</v>
       </c>
       <c r="P116" s="6" t="n">
-        <v>4770</v>
+        <v>1834</v>
       </c>
       <c r="Q116" s="6" t="n">
-        <v>82625</v>
+        <v>47673</v>
       </c>
     </row>
     <row r="117" ht="19" customHeight="1">
@@ -7887,16 +7887,16 @@
         <v>2.3</v>
       </c>
       <c r="N117" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O117" s="6" t="n">
-        <v>1610</v>
+        <v>929</v>
       </c>
       <c r="P117" s="6" t="n">
-        <v>4830</v>
+        <v>1858</v>
       </c>
       <c r="Q117" s="6" t="n">
-        <v>84235</v>
+        <v>48602</v>
       </c>
     </row>
     <row r="118" ht="19" customHeight="1">
@@ -7950,16 +7950,16 @@
         <v>2.3</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O118" s="6" t="n">
-        <v>1630</v>
+        <v>941</v>
       </c>
       <c r="P118" s="6" t="n">
-        <v>4890</v>
+        <v>1882</v>
       </c>
       <c r="Q118" s="6" t="n">
-        <v>85865</v>
+        <v>49543</v>
       </c>
     </row>
     <row r="119" ht="19" customHeight="1">
@@ -8013,16 +8013,16 @@
         <v>2.3</v>
       </c>
       <c r="N119" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O119" s="6" t="n">
-        <v>1650</v>
+        <v>952</v>
       </c>
       <c r="P119" s="6" t="n">
-        <v>4950</v>
+        <v>1904</v>
       </c>
       <c r="Q119" s="6" t="n">
-        <v>87515</v>
+        <v>50495</v>
       </c>
     </row>
     <row r="120" ht="19" customHeight="1">
@@ -8076,16 +8076,16 @@
         <v>2.3</v>
       </c>
       <c r="N120" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O120" s="6" t="n">
-        <v>1670</v>
+        <v>964</v>
       </c>
       <c r="P120" s="6" t="n">
-        <v>5010</v>
+        <v>1928</v>
       </c>
       <c r="Q120" s="6" t="n">
-        <v>89185</v>
+        <v>51459</v>
       </c>
     </row>
     <row r="121" ht="19" customHeight="1">
@@ -8139,16 +8139,16 @@
         <v>2.3</v>
       </c>
       <c r="N121" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O121" s="6" t="n">
-        <v>1690</v>
+        <v>975</v>
       </c>
       <c r="P121" s="6" t="n">
-        <v>5070</v>
+        <v>1950</v>
       </c>
       <c r="Q121" s="6" t="n">
-        <v>90875</v>
+        <v>52434</v>
       </c>
     </row>
     <row r="122" ht="19" customHeight="1">
@@ -8202,16 +8202,16 @@
         <v>2.3</v>
       </c>
       <c r="N122" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O122" s="6" t="n">
-        <v>1710</v>
+        <v>987</v>
       </c>
       <c r="P122" s="6" t="n">
-        <v>5130</v>
+        <v>1974</v>
       </c>
       <c r="Q122" s="6" t="n">
-        <v>92585</v>
+        <v>53421</v>
       </c>
     </row>
     <row r="123" ht="19" customHeight="1">
@@ -8265,16 +8265,16 @@
         <v>2.3</v>
       </c>
       <c r="N123" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O123" s="6" t="n">
-        <v>1730</v>
+        <v>998</v>
       </c>
       <c r="P123" s="6" t="n">
-        <v>5190</v>
+        <v>1996</v>
       </c>
       <c r="Q123" s="6" t="n">
-        <v>94315</v>
+        <v>54419</v>
       </c>
     </row>
     <row r="124" ht="19" customHeight="1">
@@ -8328,16 +8328,16 @@
         <v>2.3</v>
       </c>
       <c r="N124" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O124" s="6" t="n">
-        <v>1750</v>
+        <v>1010</v>
       </c>
       <c r="P124" s="6" t="n">
-        <v>5250</v>
+        <v>2020</v>
       </c>
       <c r="Q124" s="6" t="n">
-        <v>96065</v>
+        <v>55429</v>
       </c>
     </row>
     <row r="125" ht="19" customHeight="1">
@@ -8391,16 +8391,16 @@
         <v>2.3</v>
       </c>
       <c r="N125" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O125" s="6" t="n">
-        <v>1770</v>
+        <v>1021</v>
       </c>
       <c r="P125" s="6" t="n">
-        <v>5310</v>
+        <v>2042</v>
       </c>
       <c r="Q125" s="6" t="n">
-        <v>97835</v>
+        <v>56450</v>
       </c>
     </row>
     <row r="126" ht="19" customHeight="1">
@@ -8454,16 +8454,16 @@
         <v>2.3</v>
       </c>
       <c r="N126" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O126" s="6" t="n">
-        <v>1790</v>
+        <v>1033</v>
       </c>
       <c r="P126" s="6" t="n">
-        <v>5370</v>
+        <v>2066</v>
       </c>
       <c r="Q126" s="6" t="n">
-        <v>99625</v>
+        <v>57483</v>
       </c>
     </row>
     <row r="127" ht="19" customHeight="1">
@@ -8517,16 +8517,16 @@
         <v>2.3</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O127" s="6" t="n">
-        <v>1810</v>
+        <v>1044</v>
       </c>
       <c r="P127" s="6" t="n">
-        <v>5430</v>
+        <v>2088</v>
       </c>
       <c r="Q127" s="6" t="n">
-        <v>101435</v>
+        <v>58527</v>
       </c>
     </row>
     <row r="128" ht="19" customHeight="1">
@@ -8580,16 +8580,16 @@
         <v>2.3</v>
       </c>
       <c r="N128" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O128" s="6" t="n">
-        <v>1830</v>
+        <v>1056</v>
       </c>
       <c r="P128" s="6" t="n">
-        <v>5490</v>
+        <v>2112</v>
       </c>
       <c r="Q128" s="6" t="n">
-        <v>103265</v>
+        <v>59583</v>
       </c>
     </row>
     <row r="129" ht="19" customHeight="1">
@@ -8643,16 +8643,16 @@
         <v>2.3</v>
       </c>
       <c r="N129" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O129" s="6" t="n">
-        <v>1850</v>
+        <v>1067</v>
       </c>
       <c r="P129" s="6" t="n">
-        <v>5550</v>
+        <v>2134</v>
       </c>
       <c r="Q129" s="6" t="n">
-        <v>105115</v>
+        <v>60650</v>
       </c>
     </row>
     <row r="130" ht="19" customHeight="1">
@@ -8706,16 +8706,16 @@
         <v>2.3</v>
       </c>
       <c r="N130" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O130" s="6" t="n">
-        <v>1870</v>
+        <v>1079</v>
       </c>
       <c r="P130" s="6" t="n">
-        <v>5610</v>
+        <v>2158</v>
       </c>
       <c r="Q130" s="6" t="n">
-        <v>106985</v>
+        <v>61729</v>
       </c>
     </row>
     <row r="131" ht="19" customHeight="1">
@@ -8769,16 +8769,16 @@
         <v>2.3</v>
       </c>
       <c r="N131" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O131" s="6" t="n">
-        <v>1890</v>
+        <v>1091</v>
       </c>
       <c r="P131" s="6" t="n">
-        <v>5670</v>
+        <v>2182</v>
       </c>
       <c r="Q131" s="6" t="n">
-        <v>108875</v>
+        <v>62820</v>
       </c>
     </row>
     <row r="132" ht="19" customHeight="1">
@@ -8832,16 +8832,16 @@
         <v>2.3</v>
       </c>
       <c r="N132" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O132" s="6" t="n">
-        <v>1910</v>
+        <v>1102</v>
       </c>
       <c r="P132" s="6" t="n">
-        <v>5730</v>
+        <v>2204</v>
       </c>
       <c r="Q132" s="6" t="n">
-        <v>110785</v>
+        <v>63922</v>
       </c>
     </row>
     <row r="133" ht="19" customHeight="1">
@@ -8895,16 +8895,16 @@
         <v>2.3</v>
       </c>
       <c r="N133" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O133" s="6" t="n">
-        <v>1930</v>
+        <v>1114</v>
       </c>
       <c r="P133" s="6" t="n">
-        <v>5790</v>
+        <v>2228</v>
       </c>
       <c r="Q133" s="6" t="n">
-        <v>112715</v>
+        <v>65036</v>
       </c>
     </row>
     <row r="134" ht="19" customHeight="1">
@@ -8958,16 +8958,16 @@
         <v>2.3</v>
       </c>
       <c r="N134" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O134" s="6" t="n">
-        <v>1950</v>
+        <v>1125</v>
       </c>
       <c r="P134" s="6" t="n">
-        <v>5850</v>
+        <v>2250</v>
       </c>
       <c r="Q134" s="6" t="n">
-        <v>114665</v>
+        <v>66161</v>
       </c>
     </row>
     <row r="135" ht="19" customHeight="1">
@@ -9021,16 +9021,16 @@
         <v>2.3</v>
       </c>
       <c r="N135" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O135" s="6" t="n">
-        <v>1970</v>
+        <v>1137</v>
       </c>
       <c r="P135" s="6" t="n">
-        <v>5910</v>
+        <v>2274</v>
       </c>
       <c r="Q135" s="6" t="n">
-        <v>116635</v>
+        <v>67298</v>
       </c>
     </row>
     <row r="136" ht="19" customHeight="1">
@@ -9084,16 +9084,16 @@
         <v>2.3</v>
       </c>
       <c r="N136" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O136" s="6" t="n">
-        <v>1990</v>
+        <v>1148</v>
       </c>
       <c r="P136" s="6" t="n">
-        <v>5970</v>
+        <v>2296</v>
       </c>
       <c r="Q136" s="6" t="n">
-        <v>118625</v>
+        <v>68446</v>
       </c>
     </row>
     <row r="137" ht="19" customHeight="1">
@@ -9147,16 +9147,16 @@
         <v>2.3</v>
       </c>
       <c r="N137" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O137" s="6" t="n">
-        <v>2010</v>
+        <v>1160</v>
       </c>
       <c r="P137" s="6" t="n">
-        <v>6030</v>
+        <v>2320</v>
       </c>
       <c r="Q137" s="6" t="n">
-        <v>120635</v>
+        <v>69606</v>
       </c>
     </row>
     <row r="138" ht="19" customHeight="1">
@@ -9210,16 +9210,16 @@
         <v>2.3</v>
       </c>
       <c r="N138" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O138" s="6" t="n">
-        <v>2030</v>
+        <v>1171</v>
       </c>
       <c r="P138" s="6" t="n">
-        <v>6090</v>
+        <v>2342</v>
       </c>
       <c r="Q138" s="6" t="n">
-        <v>122665</v>
+        <v>70777</v>
       </c>
     </row>
     <row r="139" ht="19" customHeight="1">
@@ -9273,16 +9273,16 @@
         <v>2.3</v>
       </c>
       <c r="N139" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O139" s="6" t="n">
-        <v>2050</v>
+        <v>1183</v>
       </c>
       <c r="P139" s="6" t="n">
-        <v>6150</v>
+        <v>2366</v>
       </c>
       <c r="Q139" s="6" t="n">
-        <v>124715</v>
+        <v>71960</v>
       </c>
     </row>
     <row r="140" ht="19" customHeight="1">
@@ -9336,16 +9336,16 @@
         <v>2.3</v>
       </c>
       <c r="N140" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O140" s="6" t="n">
-        <v>2070</v>
+        <v>1194</v>
       </c>
       <c r="P140" s="6" t="n">
-        <v>6210</v>
+        <v>2388</v>
       </c>
       <c r="Q140" s="6" t="n">
-        <v>126785</v>
+        <v>73154</v>
       </c>
     </row>
     <row r="141" ht="19" customHeight="1">
@@ -9399,16 +9399,16 @@
         <v>2.3</v>
       </c>
       <c r="N141" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O141" s="6" t="n">
-        <v>2090</v>
+        <v>1206</v>
       </c>
       <c r="P141" s="6" t="n">
-        <v>6270</v>
+        <v>2412</v>
       </c>
       <c r="Q141" s="6" t="n">
-        <v>128875</v>
+        <v>74360</v>
       </c>
     </row>
     <row r="142" ht="19" customHeight="1">
@@ -9462,16 +9462,16 @@
         <v>2.3</v>
       </c>
       <c r="N142" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O142" s="6" t="n">
-        <v>2110</v>
+        <v>1217</v>
       </c>
       <c r="P142" s="6" t="n">
-        <v>6330</v>
+        <v>2434</v>
       </c>
       <c r="Q142" s="6" t="n">
-        <v>130985</v>
+        <v>75577</v>
       </c>
     </row>
     <row r="143" ht="19" customHeight="1">
@@ -9525,16 +9525,16 @@
         <v>2.3</v>
       </c>
       <c r="N143" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O143" s="6" t="n">
-        <v>2130</v>
+        <v>1229</v>
       </c>
       <c r="P143" s="6" t="n">
-        <v>6390</v>
+        <v>2458</v>
       </c>
       <c r="Q143" s="6" t="n">
-        <v>133115</v>
+        <v>76806</v>
       </c>
     </row>
     <row r="144" ht="19" customHeight="1">
@@ -9588,16 +9588,16 @@
         <v>2.3</v>
       </c>
       <c r="N144" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O144" s="6" t="n">
-        <v>2150</v>
+        <v>1241</v>
       </c>
       <c r="P144" s="6" t="n">
-        <v>6450</v>
+        <v>2482</v>
       </c>
       <c r="Q144" s="6" t="n">
-        <v>135265</v>
+        <v>78047</v>
       </c>
     </row>
     <row r="145" ht="19" customHeight="1">
@@ -9651,16 +9651,16 @@
         <v>2.3</v>
       </c>
       <c r="N145" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O145" s="6" t="n">
-        <v>2170</v>
+        <v>1252</v>
       </c>
       <c r="P145" s="6" t="n">
-        <v>6510</v>
+        <v>2504</v>
       </c>
       <c r="Q145" s="6" t="n">
-        <v>137435</v>
+        <v>79299</v>
       </c>
     </row>
     <row r="146" ht="19" customHeight="1">
@@ -9714,16 +9714,16 @@
         <v>2.3</v>
       </c>
       <c r="N146" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O146" s="6" t="n">
-        <v>2190</v>
+        <v>1264</v>
       </c>
       <c r="P146" s="6" t="n">
-        <v>6570</v>
+        <v>2528</v>
       </c>
       <c r="Q146" s="6" t="n">
-        <v>139625</v>
+        <v>80563</v>
       </c>
     </row>
     <row r="147" ht="19" customHeight="1">
@@ -9777,16 +9777,16 @@
         <v>2.3</v>
       </c>
       <c r="N147" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O147" s="6" t="n">
-        <v>2210</v>
+        <v>1275</v>
       </c>
       <c r="P147" s="6" t="n">
-        <v>6630</v>
+        <v>2550</v>
       </c>
       <c r="Q147" s="6" t="n">
-        <v>141835</v>
+        <v>81838</v>
       </c>
     </row>
     <row r="148" ht="19" customHeight="1">
@@ -9840,16 +9840,16 @@
         <v>2.3</v>
       </c>
       <c r="N148" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O148" s="6" t="n">
-        <v>2230</v>
+        <v>1287</v>
       </c>
       <c r="P148" s="6" t="n">
-        <v>6690</v>
+        <v>2574</v>
       </c>
       <c r="Q148" s="6" t="n">
-        <v>144065</v>
+        <v>83125</v>
       </c>
     </row>
     <row r="149" ht="19" customHeight="1">
@@ -9903,16 +9903,16 @@
         <v>2.3</v>
       </c>
       <c r="N149" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O149" s="6" t="n">
-        <v>2250</v>
+        <v>1298</v>
       </c>
       <c r="P149" s="6" t="n">
-        <v>6750</v>
+        <v>2596</v>
       </c>
       <c r="Q149" s="6" t="n">
-        <v>146315</v>
+        <v>84423</v>
       </c>
     </row>
     <row r="150" ht="19" customHeight="1">
@@ -9966,16 +9966,16 @@
         <v>2.3</v>
       </c>
       <c r="N150" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O150" s="6" t="n">
-        <v>2270</v>
+        <v>1310</v>
       </c>
       <c r="P150" s="6" t="n">
-        <v>6810</v>
+        <v>2620</v>
       </c>
       <c r="Q150" s="6" t="n">
-        <v>148585</v>
+        <v>85733</v>
       </c>
     </row>
     <row r="151" ht="19" customHeight="1">
@@ -10029,16 +10029,16 @@
         <v>2.3</v>
       </c>
       <c r="N151" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O151" s="6" t="n">
-        <v>2290</v>
+        <v>1321</v>
       </c>
       <c r="P151" s="6" t="n">
-        <v>6870</v>
+        <v>2642</v>
       </c>
       <c r="Q151" s="6" t="n">
-        <v>150875</v>
+        <v>87054</v>
       </c>
     </row>
   </sheetData>

--- a/Kachi_Gun/Table/Boss_Dungeon.xlsx
+++ b/Kachi_Gun/Table/Boss_Dungeon.xlsx
@@ -645,13 +645,13 @@
         <v>0</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
@@ -705,16 +705,16 @@
         <v>2.3</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>64</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
@@ -768,16 +768,16 @@
         <v>2.3</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>104</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
@@ -831,16 +831,16 @@
         <v>2.3</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>150</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
@@ -894,16 +894,16 @@
         <v>2.3</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>202</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
@@ -957,16 +957,16 @@
         <v>2.3</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>260</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -1020,16 +1020,16 @@
         <v>2.3</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>126</v>
+        <v>194</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>323</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
@@ -1083,16 +1083,16 @@
         <v>2.3</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>138</v>
+        <v>212</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>392</v>
+        <v>599</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -1146,16 +1146,16 @@
         <v>2.3</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>150</v>
+        <v>228</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>467</v>
+        <v>713</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
@@ -1209,16 +1209,16 @@
         <v>2.3</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>162</v>
+        <v>246</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>548</v>
+        <v>836</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
@@ -1272,16 +1272,16 @@
         <v>2.3</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>174</v>
+        <v>264</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>635</v>
+        <v>968</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
@@ -1335,16 +1335,16 @@
         <v>2.3</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>184</v>
+        <v>282</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>727</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
@@ -1398,16 +1398,16 @@
         <v>2.3</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>196</v>
+        <v>300</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>825</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
@@ -1461,16 +1461,16 @@
         <v>2.3</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>208</v>
+        <v>316</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>929</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
@@ -1524,16 +1524,16 @@
         <v>2.3</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>220</v>
+        <v>334</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>1039</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
@@ -1587,16 +1587,16 @@
         <v>2.3</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>115</v>
+        <v>176</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>230</v>
+        <v>352</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>1154</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
@@ -1650,16 +1650,16 @@
         <v>2.3</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>242</v>
+        <v>370</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>1275</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
@@ -1713,16 +1713,16 @@
         <v>2.3</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>254</v>
+        <v>388</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>1402</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
@@ -1776,16 +1776,16 @@
         <v>2.3</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>133</v>
+        <v>202</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>266</v>
+        <v>404</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>1535</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
@@ -1839,16 +1839,16 @@
         <v>2.3</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>138</v>
+        <v>211</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>276</v>
+        <v>422</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>1673</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
@@ -1902,16 +1902,16 @@
         <v>2.3</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>144</v>
+        <v>220</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>288</v>
+        <v>440</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>1817</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -1965,16 +1965,16 @@
         <v>2.3</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>150</v>
+        <v>229</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>1967</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
@@ -2028,16 +2028,16 @@
         <v>2.3</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>156</v>
+        <v>238</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>312</v>
+        <v>476</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>2123</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -2091,16 +2091,16 @@
         <v>2.3</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>162</v>
+        <v>246</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>324</v>
+        <v>492</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>2285</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
@@ -2154,16 +2154,16 @@
         <v>2.3</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>167</v>
+        <v>255</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>334</v>
+        <v>510</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>2452</v>
+        <v>3740</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
@@ -2217,16 +2217,16 @@
         <v>2.3</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>173</v>
+        <v>264</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>346</v>
+        <v>528</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>2625</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
@@ -2280,16 +2280,16 @@
         <v>2.3</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>179</v>
+        <v>273</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>358</v>
+        <v>546</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>2804</v>
+        <v>4277</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
@@ -2343,16 +2343,16 @@
         <v>2.3</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>185</v>
+        <v>282</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>370</v>
+        <v>564</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>2989</v>
+        <v>4559</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
@@ -2406,16 +2406,16 @@
         <v>2.3</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>190</v>
+        <v>290</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>3179</v>
+        <v>4849</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
@@ -2469,16 +2469,16 @@
         <v>2.3</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>196</v>
+        <v>299</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>392</v>
+        <v>598</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>3375</v>
+        <v>5148</v>
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
@@ -2532,16 +2532,16 @@
         <v>2.3</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>404</v>
+        <v>616</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>3577</v>
+        <v>5456</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
@@ -2595,16 +2595,16 @@
         <v>2.3</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>208</v>
+        <v>317</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>416</v>
+        <v>634</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>3785</v>
+        <v>5773</v>
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
@@ -2658,16 +2658,16 @@
         <v>2.3</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>213</v>
+        <v>326</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>426</v>
+        <v>652</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>3998</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
@@ -2721,16 +2721,16 @@
         <v>2.3</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>219</v>
+        <v>334</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>438</v>
+        <v>668</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>4217</v>
+        <v>6433</v>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
@@ -2784,16 +2784,16 @@
         <v>2.3</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>225</v>
+        <v>343</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>450</v>
+        <v>686</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>4442</v>
+        <v>6776</v>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
@@ -2847,16 +2847,16 @@
         <v>2.3</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>231</v>
+        <v>352</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>462</v>
+        <v>704</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>4673</v>
+        <v>7128</v>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
@@ -2910,16 +2910,16 @@
         <v>2.3</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>237</v>
+        <v>361</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>474</v>
+        <v>722</v>
       </c>
       <c r="Q38" s="6" t="n">
-        <v>4910</v>
+        <v>7489</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
@@ -2973,16 +2973,16 @@
         <v>2.3</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>242</v>
+        <v>370</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>484</v>
+        <v>740</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>5152</v>
+        <v>7859</v>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
@@ -3036,16 +3036,16 @@
         <v>2.3</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>248</v>
+        <v>378</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>496</v>
+        <v>756</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>5400</v>
+        <v>8237</v>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
@@ -3099,16 +3099,16 @@
         <v>2.3</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>254</v>
+        <v>387</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>508</v>
+        <v>774</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>5654</v>
+        <v>8624</v>
       </c>
     </row>
     <row r="42" ht="19" customHeight="1">
@@ -3162,16 +3162,16 @@
         <v>2.3</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>260</v>
+        <v>396</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>520</v>
+        <v>792</v>
       </c>
       <c r="Q42" s="6" t="n">
-        <v>5914</v>
+        <v>9020</v>
       </c>
     </row>
     <row r="43" ht="19" customHeight="1">
@@ -3225,16 +3225,16 @@
         <v>2.3</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>265</v>
+        <v>405</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>530</v>
+        <v>810</v>
       </c>
       <c r="Q43" s="6" t="n">
-        <v>6179</v>
+        <v>9425</v>
       </c>
     </row>
     <row r="44" ht="19" customHeight="1">
@@ -3288,16 +3288,16 @@
         <v>2.3</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>271</v>
+        <v>414</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>542</v>
+        <v>828</v>
       </c>
       <c r="Q44" s="6" t="n">
-        <v>6450</v>
+        <v>9839</v>
       </c>
     </row>
     <row r="45" ht="19" customHeight="1">
@@ -3351,16 +3351,16 @@
         <v>2.3</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>277</v>
+        <v>422</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>554</v>
+        <v>844</v>
       </c>
       <c r="Q45" s="6" t="n">
-        <v>6727</v>
+        <v>10261</v>
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
@@ -3414,16 +3414,16 @@
         <v>2.3</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>283</v>
+        <v>431</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>566</v>
+        <v>862</v>
       </c>
       <c r="Q46" s="6" t="n">
-        <v>7010</v>
+        <v>10692</v>
       </c>
     </row>
     <row r="47" ht="19" customHeight="1">
@@ -3477,16 +3477,16 @@
         <v>2.3</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>288</v>
+        <v>440</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>576</v>
+        <v>880</v>
       </c>
       <c r="Q47" s="6" t="n">
-        <v>7298</v>
+        <v>11132</v>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
@@ -3540,16 +3540,16 @@
         <v>2.3</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>294</v>
+        <v>449</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>588</v>
+        <v>898</v>
       </c>
       <c r="Q48" s="6" t="n">
-        <v>7592</v>
+        <v>11581</v>
       </c>
     </row>
     <row r="49" ht="19" customHeight="1">
@@ -3603,16 +3603,16 @@
         <v>2.3</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>600</v>
+        <v>916</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>7892</v>
+        <v>12039</v>
       </c>
     </row>
     <row r="50" ht="19" customHeight="1">
@@ -3666,16 +3666,16 @@
         <v>2.3</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>306</v>
+        <v>466</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>612</v>
+        <v>932</v>
       </c>
       <c r="Q50" s="6" t="n">
-        <v>8198</v>
+        <v>12505</v>
       </c>
     </row>
     <row r="51" ht="19" customHeight="1">
@@ -3729,16 +3729,16 @@
         <v>2.3</v>
       </c>
       <c r="N51" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>312</v>
+        <v>475</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>624</v>
+        <v>950</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>8510</v>
+        <v>12980</v>
       </c>
     </row>
     <row r="52" ht="19" customHeight="1">
@@ -3792,16 +3792,16 @@
         <v>2.3</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>320</v>
+        <v>488</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>640</v>
+        <v>976</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>8830</v>
+        <v>13468</v>
       </c>
     </row>
     <row r="53" ht="19" customHeight="1">
@@ -3855,16 +3855,16 @@
         <v>2.3</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>329</v>
+        <v>502</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>658</v>
+        <v>1004</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>9159</v>
+        <v>13970</v>
       </c>
     </row>
     <row r="54" ht="19" customHeight="1">
@@ -3918,16 +3918,16 @@
         <v>2.3</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>338</v>
+        <v>515</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>676</v>
+        <v>1030</v>
       </c>
       <c r="Q54" s="6" t="n">
-        <v>9497</v>
+        <v>14485</v>
       </c>
     </row>
     <row r="55" ht="19" customHeight="1">
@@ -3981,16 +3981,16 @@
         <v>2.3</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>346</v>
+        <v>528</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>692</v>
+        <v>1056</v>
       </c>
       <c r="Q55" s="6" t="n">
-        <v>9843</v>
+        <v>15013</v>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
@@ -4044,16 +4044,16 @@
         <v>2.3</v>
       </c>
       <c r="N56" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>355</v>
+        <v>541</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>710</v>
+        <v>1082</v>
       </c>
       <c r="Q56" s="6" t="n">
-        <v>10198</v>
+        <v>15554</v>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
@@ -4107,16 +4107,16 @@
         <v>2.3</v>
       </c>
       <c r="N57" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>364</v>
+        <v>554</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>728</v>
+        <v>1108</v>
       </c>
       <c r="Q57" s="6" t="n">
-        <v>10562</v>
+        <v>16108</v>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
@@ -4170,16 +4170,16 @@
         <v>2.3</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>372</v>
+        <v>568</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>744</v>
+        <v>1136</v>
       </c>
       <c r="Q58" s="6" t="n">
-        <v>10934</v>
+        <v>16676</v>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
@@ -4233,16 +4233,16 @@
         <v>2.3</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>381</v>
+        <v>581</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>762</v>
+        <v>1162</v>
       </c>
       <c r="Q59" s="6" t="n">
-        <v>11315</v>
+        <v>17257</v>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
@@ -4296,16 +4296,16 @@
         <v>2.3</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>389</v>
+        <v>594</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>778</v>
+        <v>1188</v>
       </c>
       <c r="Q60" s="6" t="n">
-        <v>11704</v>
+        <v>17851</v>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
@@ -4359,16 +4359,16 @@
         <v>2.3</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>398</v>
+        <v>607</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>796</v>
+        <v>1214</v>
       </c>
       <c r="Q61" s="6" t="n">
-        <v>12102</v>
+        <v>18458</v>
       </c>
     </row>
     <row r="62" ht="19" customHeight="1">
@@ -4422,16 +4422,16 @@
         <v>2.3</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>407</v>
+        <v>620</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>814</v>
+        <v>1240</v>
       </c>
       <c r="Q62" s="6" t="n">
-        <v>12509</v>
+        <v>19078</v>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
@@ -4485,16 +4485,16 @@
         <v>2.3</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>415</v>
+        <v>634</v>
       </c>
       <c r="P63" s="6" t="n">
-        <v>830</v>
+        <v>1268</v>
       </c>
       <c r="Q63" s="6" t="n">
-        <v>12924</v>
+        <v>19712</v>
       </c>
     </row>
     <row r="64" ht="19" customHeight="1">
@@ -4548,16 +4548,16 @@
         <v>2.3</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>424</v>
+        <v>647</v>
       </c>
       <c r="P64" s="6" t="n">
-        <v>848</v>
+        <v>1294</v>
       </c>
       <c r="Q64" s="6" t="n">
-        <v>13348</v>
+        <v>20359</v>
       </c>
     </row>
     <row r="65" ht="19" customHeight="1">
@@ -4611,16 +4611,16 @@
         <v>2.3</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>433</v>
+        <v>660</v>
       </c>
       <c r="P65" s="6" t="n">
-        <v>866</v>
+        <v>1320</v>
       </c>
       <c r="Q65" s="6" t="n">
-        <v>13781</v>
+        <v>21019</v>
       </c>
     </row>
     <row r="66" ht="19" customHeight="1">
@@ -4674,16 +4674,16 @@
         <v>2.3</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>441</v>
+        <v>673</v>
       </c>
       <c r="P66" s="6" t="n">
-        <v>882</v>
+        <v>1346</v>
       </c>
       <c r="Q66" s="6" t="n">
-        <v>14222</v>
+        <v>21692</v>
       </c>
     </row>
     <row r="67" ht="19" customHeight="1">
@@ -4737,16 +4737,16 @@
         <v>2.3</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>450</v>
+        <v>686</v>
       </c>
       <c r="P67" s="6" t="n">
-        <v>900</v>
+        <v>1372</v>
       </c>
       <c r="Q67" s="6" t="n">
-        <v>14672</v>
+        <v>22378</v>
       </c>
     </row>
     <row r="68" ht="19" customHeight="1">
@@ -4800,16 +4800,16 @@
         <v>2.3</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>459</v>
+        <v>700</v>
       </c>
       <c r="P68" s="6" t="n">
-        <v>918</v>
+        <v>1400</v>
       </c>
       <c r="Q68" s="6" t="n">
-        <v>15131</v>
+        <v>23078</v>
       </c>
     </row>
     <row r="69" ht="19" customHeight="1">
@@ -4863,16 +4863,16 @@
         <v>2.3</v>
       </c>
       <c r="N69" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>467</v>
+        <v>713</v>
       </c>
       <c r="P69" s="6" t="n">
-        <v>934</v>
+        <v>1426</v>
       </c>
       <c r="Q69" s="6" t="n">
-        <v>15598</v>
+        <v>23791</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1">
@@ -4926,16 +4926,16 @@
         <v>2.3</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>476</v>
+        <v>726</v>
       </c>
       <c r="P70" s="6" t="n">
-        <v>952</v>
+        <v>1452</v>
       </c>
       <c r="Q70" s="6" t="n">
-        <v>16074</v>
+        <v>24517</v>
       </c>
     </row>
     <row r="71" ht="19" customHeight="1">
@@ -4989,16 +4989,16 @@
         <v>2.3</v>
       </c>
       <c r="N71" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>485</v>
+        <v>739</v>
       </c>
       <c r="P71" s="6" t="n">
-        <v>970</v>
+        <v>1478</v>
       </c>
       <c r="Q71" s="6" t="n">
-        <v>16559</v>
+        <v>25256</v>
       </c>
     </row>
     <row r="72" ht="19" customHeight="1">
@@ -5052,16 +5052,16 @@
         <v>2.3</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>493</v>
+        <v>752</v>
       </c>
       <c r="P72" s="6" t="n">
-        <v>986</v>
+        <v>1504</v>
       </c>
       <c r="Q72" s="6" t="n">
-        <v>17052</v>
+        <v>26008</v>
       </c>
     </row>
     <row r="73" ht="19" customHeight="1">
@@ -5115,16 +5115,16 @@
         <v>2.3</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>502</v>
+        <v>766</v>
       </c>
       <c r="P73" s="6" t="n">
-        <v>1004</v>
+        <v>1532</v>
       </c>
       <c r="Q73" s="6" t="n">
-        <v>17554</v>
+        <v>26774</v>
       </c>
     </row>
     <row r="74" ht="19" customHeight="1">
@@ -5178,16 +5178,16 @@
         <v>2.3</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>511</v>
+        <v>779</v>
       </c>
       <c r="P74" s="6" t="n">
-        <v>1022</v>
+        <v>1558</v>
       </c>
       <c r="Q74" s="6" t="n">
-        <v>18065</v>
+        <v>27553</v>
       </c>
     </row>
     <row r="75" ht="19" customHeight="1">
@@ -5241,16 +5241,16 @@
         <v>2.3</v>
       </c>
       <c r="N75" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>519</v>
+        <v>792</v>
       </c>
       <c r="P75" s="6" t="n">
-        <v>1038</v>
+        <v>1584</v>
       </c>
       <c r="Q75" s="6" t="n">
-        <v>18584</v>
+        <v>28345</v>
       </c>
     </row>
     <row r="76" ht="19" customHeight="1">
@@ -5304,16 +5304,16 @@
         <v>2.3</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>528</v>
+        <v>805</v>
       </c>
       <c r="P76" s="6" t="n">
-        <v>1056</v>
+        <v>1610</v>
       </c>
       <c r="Q76" s="6" t="n">
-        <v>19112</v>
+        <v>29150</v>
       </c>
     </row>
     <row r="77" ht="19" customHeight="1">
@@ -5367,16 +5367,16 @@
         <v>2.3</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>537</v>
+        <v>818</v>
       </c>
       <c r="P77" s="6" t="n">
-        <v>1074</v>
+        <v>1636</v>
       </c>
       <c r="Q77" s="6" t="n">
-        <v>19649</v>
+        <v>29968</v>
       </c>
     </row>
     <row r="78" ht="19" customHeight="1">
@@ -5430,16 +5430,16 @@
         <v>2.3</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>545</v>
+        <v>832</v>
       </c>
       <c r="P78" s="6" t="n">
-        <v>1090</v>
+        <v>1664</v>
       </c>
       <c r="Q78" s="6" t="n">
-        <v>20194</v>
+        <v>30800</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1">
@@ -5493,16 +5493,16 @@
         <v>2.3</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>554</v>
+        <v>845</v>
       </c>
       <c r="P79" s="6" t="n">
-        <v>1108</v>
+        <v>1690</v>
       </c>
       <c r="Q79" s="6" t="n">
-        <v>20748</v>
+        <v>31645</v>
       </c>
     </row>
     <row r="80" ht="19" customHeight="1">
@@ -5556,16 +5556,16 @@
         <v>2.3</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>563</v>
+        <v>858</v>
       </c>
       <c r="P80" s="6" t="n">
-        <v>1126</v>
+        <v>1716</v>
       </c>
       <c r="Q80" s="6" t="n">
-        <v>21311</v>
+        <v>32503</v>
       </c>
     </row>
     <row r="81" ht="19" customHeight="1">
@@ -5619,16 +5619,16 @@
         <v>2.3</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>571</v>
+        <v>871</v>
       </c>
       <c r="P81" s="6" t="n">
-        <v>1142</v>
+        <v>1742</v>
       </c>
       <c r="Q81" s="6" t="n">
-        <v>21882</v>
+        <v>33374</v>
       </c>
     </row>
     <row r="82" ht="19" customHeight="1">
@@ -5682,16 +5682,16 @@
         <v>2.3</v>
       </c>
       <c r="N82" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O82" s="6" t="n">
-        <v>580</v>
+        <v>884</v>
       </c>
       <c r="P82" s="6" t="n">
-        <v>1160</v>
+        <v>1768</v>
       </c>
       <c r="Q82" s="6" t="n">
-        <v>22462</v>
+        <v>34258</v>
       </c>
     </row>
     <row r="83" ht="19" customHeight="1">
@@ -5745,16 +5745,16 @@
         <v>2.3</v>
       </c>
       <c r="N83" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O83" s="6" t="n">
-        <v>589</v>
+        <v>898</v>
       </c>
       <c r="P83" s="6" t="n">
-        <v>1178</v>
+        <v>1796</v>
       </c>
       <c r="Q83" s="6" t="n">
-        <v>23051</v>
+        <v>35156</v>
       </c>
     </row>
     <row r="84" ht="19" customHeight="1">
@@ -5808,16 +5808,16 @@
         <v>2.3</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O84" s="6" t="n">
-        <v>597</v>
+        <v>911</v>
       </c>
       <c r="P84" s="6" t="n">
-        <v>1194</v>
+        <v>1822</v>
       </c>
       <c r="Q84" s="6" t="n">
-        <v>23648</v>
+        <v>36067</v>
       </c>
     </row>
     <row r="85" ht="19" customHeight="1">
@@ -5871,16 +5871,16 @@
         <v>2.3</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O85" s="6" t="n">
-        <v>606</v>
+        <v>924</v>
       </c>
       <c r="P85" s="6" t="n">
-        <v>1212</v>
+        <v>1848</v>
       </c>
       <c r="Q85" s="6" t="n">
-        <v>24254</v>
+        <v>36991</v>
       </c>
     </row>
     <row r="86" ht="19" customHeight="1">
@@ -5934,16 +5934,16 @@
         <v>2.3</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O86" s="6" t="n">
-        <v>615</v>
+        <v>937</v>
       </c>
       <c r="P86" s="6" t="n">
-        <v>1230</v>
+        <v>1874</v>
       </c>
       <c r="Q86" s="6" t="n">
-        <v>24869</v>
+        <v>37928</v>
       </c>
     </row>
     <row r="87" ht="19" customHeight="1">
@@ -5997,16 +5997,16 @@
         <v>2.3</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O87" s="6" t="n">
-        <v>623</v>
+        <v>950</v>
       </c>
       <c r="P87" s="6" t="n">
-        <v>1246</v>
+        <v>1900</v>
       </c>
       <c r="Q87" s="6" t="n">
-        <v>25492</v>
+        <v>38878</v>
       </c>
     </row>
     <row r="88" ht="19" customHeight="1">
@@ -6060,16 +6060,16 @@
         <v>2.3</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O88" s="6" t="n">
-        <v>632</v>
+        <v>964</v>
       </c>
       <c r="P88" s="6" t="n">
-        <v>1264</v>
+        <v>1928</v>
       </c>
       <c r="Q88" s="6" t="n">
-        <v>26124</v>
+        <v>39842</v>
       </c>
     </row>
     <row r="89" ht="19" customHeight="1">
@@ -6123,16 +6123,16 @@
         <v>2.3</v>
       </c>
       <c r="N89" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O89" s="6" t="n">
-        <v>640</v>
+        <v>977</v>
       </c>
       <c r="P89" s="6" t="n">
-        <v>1280</v>
+        <v>1954</v>
       </c>
       <c r="Q89" s="6" t="n">
-        <v>26764</v>
+        <v>40819</v>
       </c>
     </row>
     <row r="90" ht="19" customHeight="1">
@@ -6186,16 +6186,16 @@
         <v>2.3</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O90" s="6" t="n">
-        <v>649</v>
+        <v>990</v>
       </c>
       <c r="P90" s="6" t="n">
-        <v>1298</v>
+        <v>1980</v>
       </c>
       <c r="Q90" s="6" t="n">
-        <v>27413</v>
+        <v>41809</v>
       </c>
     </row>
     <row r="91" ht="19" customHeight="1">
@@ -6249,16 +6249,16 @@
         <v>2.3</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O91" s="6" t="n">
-        <v>658</v>
+        <v>1003</v>
       </c>
       <c r="P91" s="6" t="n">
-        <v>1316</v>
+        <v>2006</v>
       </c>
       <c r="Q91" s="6" t="n">
-        <v>28071</v>
+        <v>42812</v>
       </c>
     </row>
     <row r="92" ht="19" customHeight="1">
@@ -6312,16 +6312,16 @@
         <v>2.3</v>
       </c>
       <c r="N92" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O92" s="6" t="n">
-        <v>666</v>
+        <v>1016</v>
       </c>
       <c r="P92" s="6" t="n">
-        <v>1332</v>
+        <v>2032</v>
       </c>
       <c r="Q92" s="6" t="n">
-        <v>28737</v>
+        <v>43828</v>
       </c>
     </row>
     <row r="93" ht="19" customHeight="1">
@@ -6375,16 +6375,16 @@
         <v>2.3</v>
       </c>
       <c r="N93" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O93" s="6" t="n">
-        <v>675</v>
+        <v>1030</v>
       </c>
       <c r="P93" s="6" t="n">
-        <v>1350</v>
+        <v>2060</v>
       </c>
       <c r="Q93" s="6" t="n">
-        <v>29412</v>
+        <v>44858</v>
       </c>
     </row>
     <row r="94" ht="19" customHeight="1">
@@ -6438,16 +6438,16 @@
         <v>2.3</v>
       </c>
       <c r="N94" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O94" s="6" t="n">
-        <v>684</v>
+        <v>1043</v>
       </c>
       <c r="P94" s="6" t="n">
-        <v>1368</v>
+        <v>2086</v>
       </c>
       <c r="Q94" s="6" t="n">
-        <v>30096</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="95" ht="19" customHeight="1">
@@ -6501,16 +6501,16 @@
         <v>2.3</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O95" s="6" t="n">
-        <v>692</v>
+        <v>1056</v>
       </c>
       <c r="P95" s="6" t="n">
-        <v>1384</v>
+        <v>2112</v>
       </c>
       <c r="Q95" s="6" t="n">
-        <v>30788</v>
+        <v>46957</v>
       </c>
     </row>
     <row r="96" ht="19" customHeight="1">
@@ -6564,16 +6564,16 @@
         <v>2.3</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O96" s="6" t="n">
-        <v>701</v>
+        <v>1069</v>
       </c>
       <c r="P96" s="6" t="n">
-        <v>1402</v>
+        <v>2138</v>
       </c>
       <c r="Q96" s="6" t="n">
-        <v>31489</v>
+        <v>48026</v>
       </c>
     </row>
     <row r="97" ht="19" customHeight="1">
@@ -6627,16 +6627,16 @@
         <v>2.3</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O97" s="6" t="n">
-        <v>710</v>
+        <v>1082</v>
       </c>
       <c r="P97" s="6" t="n">
-        <v>1420</v>
+        <v>2164</v>
       </c>
       <c r="Q97" s="6" t="n">
-        <v>32199</v>
+        <v>49108</v>
       </c>
     </row>
     <row r="98" ht="19" customHeight="1">
@@ -6690,16 +6690,16 @@
         <v>2.3</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O98" s="6" t="n">
-        <v>718</v>
+        <v>1096</v>
       </c>
       <c r="P98" s="6" t="n">
-        <v>1436</v>
+        <v>2192</v>
       </c>
       <c r="Q98" s="6" t="n">
-        <v>32917</v>
+        <v>50204</v>
       </c>
     </row>
     <row r="99" ht="19" customHeight="1">
@@ -6753,16 +6753,16 @@
         <v>2.3</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O99" s="6" t="n">
-        <v>727</v>
+        <v>1109</v>
       </c>
       <c r="P99" s="6" t="n">
-        <v>1454</v>
+        <v>2218</v>
       </c>
       <c r="Q99" s="6" t="n">
-        <v>33644</v>
+        <v>51313</v>
       </c>
     </row>
     <row r="100" ht="19" customHeight="1">
@@ -6816,16 +6816,16 @@
         <v>2.3</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O100" s="6" t="n">
-        <v>736</v>
+        <v>1122</v>
       </c>
       <c r="P100" s="6" t="n">
-        <v>1472</v>
+        <v>2244</v>
       </c>
       <c r="Q100" s="6" t="n">
-        <v>34380</v>
+        <v>52435</v>
       </c>
     </row>
     <row r="101" ht="19" customHeight="1">
@@ -6879,16 +6879,16 @@
         <v>2.3</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O101" s="6" t="n">
-        <v>744</v>
+        <v>1135</v>
       </c>
       <c r="P101" s="6" t="n">
-        <v>1488</v>
+        <v>2270</v>
       </c>
       <c r="Q101" s="6" t="n">
-        <v>35124</v>
+        <v>53570</v>
       </c>
     </row>
     <row r="102" ht="19" customHeight="1">
@@ -6942,16 +6942,16 @@
         <v>2.3</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O102" s="6" t="n">
-        <v>756</v>
+        <v>1153</v>
       </c>
       <c r="P102" s="6" t="n">
-        <v>1512</v>
+        <v>2306</v>
       </c>
       <c r="Q102" s="6" t="n">
-        <v>35880</v>
+        <v>54723</v>
       </c>
     </row>
     <row r="103" ht="19" customHeight="1">
@@ -7005,16 +7005,16 @@
         <v>2.3</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O103" s="6" t="n">
-        <v>767</v>
+        <v>1170</v>
       </c>
       <c r="P103" s="6" t="n">
-        <v>1534</v>
+        <v>2340</v>
       </c>
       <c r="Q103" s="6" t="n">
-        <v>36647</v>
+        <v>55893</v>
       </c>
     </row>
     <row r="104" ht="19" customHeight="1">
@@ -7068,16 +7068,16 @@
         <v>2.3</v>
       </c>
       <c r="N104" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O104" s="6" t="n">
-        <v>779</v>
+        <v>1188</v>
       </c>
       <c r="P104" s="6" t="n">
-        <v>1558</v>
+        <v>2376</v>
       </c>
       <c r="Q104" s="6" t="n">
-        <v>37426</v>
+        <v>57081</v>
       </c>
     </row>
     <row r="105" ht="19" customHeight="1">
@@ -7131,16 +7131,16 @@
         <v>2.3</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O105" s="6" t="n">
-        <v>790</v>
+        <v>1206</v>
       </c>
       <c r="P105" s="6" t="n">
-        <v>1580</v>
+        <v>2412</v>
       </c>
       <c r="Q105" s="6" t="n">
-        <v>38216</v>
+        <v>58287</v>
       </c>
     </row>
     <row r="106" ht="19" customHeight="1">
@@ -7194,16 +7194,16 @@
         <v>2.3</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O106" s="6" t="n">
-        <v>802</v>
+        <v>1223</v>
       </c>
       <c r="P106" s="6" t="n">
-        <v>1604</v>
+        <v>2446</v>
       </c>
       <c r="Q106" s="6" t="n">
-        <v>39018</v>
+        <v>59510</v>
       </c>
     </row>
     <row r="107" ht="19" customHeight="1">
@@ -7257,16 +7257,16 @@
         <v>2.3</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O107" s="6" t="n">
-        <v>814</v>
+        <v>1241</v>
       </c>
       <c r="P107" s="6" t="n">
-        <v>1628</v>
+        <v>2482</v>
       </c>
       <c r="Q107" s="6" t="n">
-        <v>39832</v>
+        <v>60751</v>
       </c>
     </row>
     <row r="108" ht="19" customHeight="1">
@@ -7320,16 +7320,16 @@
         <v>2.3</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O108" s="6" t="n">
-        <v>825</v>
+        <v>1258</v>
       </c>
       <c r="P108" s="6" t="n">
-        <v>1650</v>
+        <v>2516</v>
       </c>
       <c r="Q108" s="6" t="n">
-        <v>40657</v>
+        <v>62009</v>
       </c>
     </row>
     <row r="109" ht="19" customHeight="1">
@@ -7383,16 +7383,16 @@
         <v>2.3</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O109" s="6" t="n">
-        <v>837</v>
+        <v>1276</v>
       </c>
       <c r="P109" s="6" t="n">
-        <v>1674</v>
+        <v>2552</v>
       </c>
       <c r="Q109" s="6" t="n">
-        <v>41494</v>
+        <v>63285</v>
       </c>
     </row>
     <row r="110" ht="19" customHeight="1">
@@ -7446,16 +7446,16 @@
         <v>2.3</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O110" s="6" t="n">
-        <v>848</v>
+        <v>1294</v>
       </c>
       <c r="P110" s="6" t="n">
-        <v>1696</v>
+        <v>2588</v>
       </c>
       <c r="Q110" s="6" t="n">
-        <v>42342</v>
+        <v>64579</v>
       </c>
     </row>
     <row r="111" ht="19" customHeight="1">
@@ -7509,16 +7509,16 @@
         <v>2.3</v>
       </c>
       <c r="N111" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O111" s="6" t="n">
-        <v>860</v>
+        <v>1311</v>
       </c>
       <c r="P111" s="6" t="n">
-        <v>1720</v>
+        <v>2622</v>
       </c>
       <c r="Q111" s="6" t="n">
-        <v>43202</v>
+        <v>65890</v>
       </c>
     </row>
     <row r="112" ht="19" customHeight="1">
@@ -7572,16 +7572,16 @@
         <v>2.3</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O112" s="6" t="n">
-        <v>871</v>
+        <v>1329</v>
       </c>
       <c r="P112" s="6" t="n">
-        <v>1742</v>
+        <v>2658</v>
       </c>
       <c r="Q112" s="6" t="n">
-        <v>44073</v>
+        <v>67219</v>
       </c>
     </row>
     <row r="113" ht="19" customHeight="1">
@@ -7635,16 +7635,16 @@
         <v>2.3</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O113" s="6" t="n">
-        <v>883</v>
+        <v>1346</v>
       </c>
       <c r="P113" s="6" t="n">
-        <v>1766</v>
+        <v>2692</v>
       </c>
       <c r="Q113" s="6" t="n">
-        <v>44956</v>
+        <v>68565</v>
       </c>
     </row>
     <row r="114" ht="19" customHeight="1">
@@ -7698,16 +7698,16 @@
         <v>2.3</v>
       </c>
       <c r="N114" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O114" s="6" t="n">
-        <v>894</v>
+        <v>1364</v>
       </c>
       <c r="P114" s="6" t="n">
-        <v>1788</v>
+        <v>2728</v>
       </c>
       <c r="Q114" s="6" t="n">
-        <v>45850</v>
+        <v>69929</v>
       </c>
     </row>
     <row r="115" ht="19" customHeight="1">
@@ -7761,16 +7761,16 @@
         <v>2.3</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O115" s="6" t="n">
-        <v>906</v>
+        <v>1382</v>
       </c>
       <c r="P115" s="6" t="n">
-        <v>1812</v>
+        <v>2764</v>
       </c>
       <c r="Q115" s="6" t="n">
-        <v>46756</v>
+        <v>71311</v>
       </c>
     </row>
     <row r="116" ht="19" customHeight="1">
@@ -7824,16 +7824,16 @@
         <v>2.3</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O116" s="6" t="n">
-        <v>917</v>
+        <v>1399</v>
       </c>
       <c r="P116" s="6" t="n">
-        <v>1834</v>
+        <v>2798</v>
       </c>
       <c r="Q116" s="6" t="n">
-        <v>47673</v>
+        <v>72710</v>
       </c>
     </row>
     <row r="117" ht="19" customHeight="1">
@@ -7887,16 +7887,16 @@
         <v>2.3</v>
       </c>
       <c r="N117" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O117" s="6" t="n">
-        <v>929</v>
+        <v>1417</v>
       </c>
       <c r="P117" s="6" t="n">
-        <v>1858</v>
+        <v>2834</v>
       </c>
       <c r="Q117" s="6" t="n">
-        <v>48602</v>
+        <v>74127</v>
       </c>
     </row>
     <row r="118" ht="19" customHeight="1">
@@ -7950,16 +7950,16 @@
         <v>2.3</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O118" s="6" t="n">
-        <v>941</v>
+        <v>1434</v>
       </c>
       <c r="P118" s="6" t="n">
-        <v>1882</v>
+        <v>2868</v>
       </c>
       <c r="Q118" s="6" t="n">
-        <v>49543</v>
+        <v>75561</v>
       </c>
     </row>
     <row r="119" ht="19" customHeight="1">
@@ -8013,16 +8013,16 @@
         <v>2.3</v>
       </c>
       <c r="N119" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O119" s="6" t="n">
-        <v>952</v>
+        <v>1452</v>
       </c>
       <c r="P119" s="6" t="n">
-        <v>1904</v>
+        <v>2904</v>
       </c>
       <c r="Q119" s="6" t="n">
-        <v>50495</v>
+        <v>77013</v>
       </c>
     </row>
     <row r="120" ht="19" customHeight="1">
@@ -8076,16 +8076,16 @@
         <v>2.3</v>
       </c>
       <c r="N120" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O120" s="6" t="n">
-        <v>964</v>
+        <v>1470</v>
       </c>
       <c r="P120" s="6" t="n">
-        <v>1928</v>
+        <v>2940</v>
       </c>
       <c r="Q120" s="6" t="n">
-        <v>51459</v>
+        <v>78483</v>
       </c>
     </row>
     <row r="121" ht="19" customHeight="1">
@@ -8139,16 +8139,16 @@
         <v>2.3</v>
       </c>
       <c r="N121" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O121" s="6" t="n">
-        <v>975</v>
+        <v>1487</v>
       </c>
       <c r="P121" s="6" t="n">
-        <v>1950</v>
+        <v>2974</v>
       </c>
       <c r="Q121" s="6" t="n">
-        <v>52434</v>
+        <v>79970</v>
       </c>
     </row>
     <row r="122" ht="19" customHeight="1">
@@ -8202,16 +8202,16 @@
         <v>2.3</v>
       </c>
       <c r="N122" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O122" s="6" t="n">
-        <v>987</v>
+        <v>1505</v>
       </c>
       <c r="P122" s="6" t="n">
-        <v>1974</v>
+        <v>3010</v>
       </c>
       <c r="Q122" s="6" t="n">
-        <v>53421</v>
+        <v>81475</v>
       </c>
     </row>
     <row r="123" ht="19" customHeight="1">
@@ -8265,16 +8265,16 @@
         <v>2.3</v>
       </c>
       <c r="N123" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O123" s="6" t="n">
-        <v>998</v>
+        <v>1522</v>
       </c>
       <c r="P123" s="6" t="n">
-        <v>1996</v>
+        <v>3044</v>
       </c>
       <c r="Q123" s="6" t="n">
-        <v>54419</v>
+        <v>82997</v>
       </c>
     </row>
     <row r="124" ht="19" customHeight="1">
@@ -8328,16 +8328,16 @@
         <v>2.3</v>
       </c>
       <c r="N124" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O124" s="6" t="n">
-        <v>1010</v>
+        <v>1540</v>
       </c>
       <c r="P124" s="6" t="n">
-        <v>2020</v>
+        <v>3080</v>
       </c>
       <c r="Q124" s="6" t="n">
-        <v>55429</v>
+        <v>84537</v>
       </c>
     </row>
     <row r="125" ht="19" customHeight="1">
@@ -8391,16 +8391,16 @@
         <v>2.3</v>
       </c>
       <c r="N125" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O125" s="6" t="n">
-        <v>1021</v>
+        <v>1558</v>
       </c>
       <c r="P125" s="6" t="n">
-        <v>2042</v>
+        <v>3116</v>
       </c>
       <c r="Q125" s="6" t="n">
-        <v>56450</v>
+        <v>86095</v>
       </c>
     </row>
     <row r="126" ht="19" customHeight="1">
@@ -8454,16 +8454,16 @@
         <v>2.3</v>
       </c>
       <c r="N126" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O126" s="6" t="n">
-        <v>1033</v>
+        <v>1575</v>
       </c>
       <c r="P126" s="6" t="n">
-        <v>2066</v>
+        <v>3150</v>
       </c>
       <c r="Q126" s="6" t="n">
-        <v>57483</v>
+        <v>87670</v>
       </c>
     </row>
     <row r="127" ht="19" customHeight="1">
@@ -8517,16 +8517,16 @@
         <v>2.3</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O127" s="6" t="n">
-        <v>1044</v>
+        <v>1593</v>
       </c>
       <c r="P127" s="6" t="n">
-        <v>2088</v>
+        <v>3186</v>
       </c>
       <c r="Q127" s="6" t="n">
-        <v>58527</v>
+        <v>89263</v>
       </c>
     </row>
     <row r="128" ht="19" customHeight="1">
@@ -8580,16 +8580,16 @@
         <v>2.3</v>
       </c>
       <c r="N128" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O128" s="6" t="n">
-        <v>1056</v>
+        <v>1610</v>
       </c>
       <c r="P128" s="6" t="n">
-        <v>2112</v>
+        <v>3220</v>
       </c>
       <c r="Q128" s="6" t="n">
-        <v>59583</v>
+        <v>90873</v>
       </c>
     </row>
     <row r="129" ht="19" customHeight="1">
@@ -8643,16 +8643,16 @@
         <v>2.3</v>
       </c>
       <c r="N129" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O129" s="6" t="n">
-        <v>1067</v>
+        <v>1628</v>
       </c>
       <c r="P129" s="6" t="n">
-        <v>2134</v>
+        <v>3256</v>
       </c>
       <c r="Q129" s="6" t="n">
-        <v>60650</v>
+        <v>92501</v>
       </c>
     </row>
     <row r="130" ht="19" customHeight="1">
@@ -8706,16 +8706,16 @@
         <v>2.3</v>
       </c>
       <c r="N130" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O130" s="6" t="n">
-        <v>1079</v>
+        <v>1646</v>
       </c>
       <c r="P130" s="6" t="n">
-        <v>2158</v>
+        <v>3292</v>
       </c>
       <c r="Q130" s="6" t="n">
-        <v>61729</v>
+        <v>94147</v>
       </c>
     </row>
     <row r="131" ht="19" customHeight="1">
@@ -8769,16 +8769,16 @@
         <v>2.3</v>
       </c>
       <c r="N131" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O131" s="6" t="n">
-        <v>1091</v>
+        <v>1663</v>
       </c>
       <c r="P131" s="6" t="n">
-        <v>2182</v>
+        <v>3326</v>
       </c>
       <c r="Q131" s="6" t="n">
-        <v>62820</v>
+        <v>95810</v>
       </c>
     </row>
     <row r="132" ht="19" customHeight="1">
@@ -8832,16 +8832,16 @@
         <v>2.3</v>
       </c>
       <c r="N132" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O132" s="6" t="n">
-        <v>1102</v>
+        <v>1681</v>
       </c>
       <c r="P132" s="6" t="n">
-        <v>2204</v>
+        <v>3362</v>
       </c>
       <c r="Q132" s="6" t="n">
-        <v>63922</v>
+        <v>97491</v>
       </c>
     </row>
     <row r="133" ht="19" customHeight="1">
@@ -8895,16 +8895,16 @@
         <v>2.3</v>
       </c>
       <c r="N133" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O133" s="6" t="n">
-        <v>1114</v>
+        <v>1698</v>
       </c>
       <c r="P133" s="6" t="n">
-        <v>2228</v>
+        <v>3396</v>
       </c>
       <c r="Q133" s="6" t="n">
-        <v>65036</v>
+        <v>99189</v>
       </c>
     </row>
     <row r="134" ht="19" customHeight="1">
@@ -8958,16 +8958,16 @@
         <v>2.3</v>
       </c>
       <c r="N134" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O134" s="6" t="n">
-        <v>1125</v>
+        <v>1716</v>
       </c>
       <c r="P134" s="6" t="n">
-        <v>2250</v>
+        <v>3432</v>
       </c>
       <c r="Q134" s="6" t="n">
-        <v>66161</v>
+        <v>100905</v>
       </c>
     </row>
     <row r="135" ht="19" customHeight="1">
@@ -9021,16 +9021,16 @@
         <v>2.3</v>
       </c>
       <c r="N135" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O135" s="6" t="n">
-        <v>1137</v>
+        <v>1734</v>
       </c>
       <c r="P135" s="6" t="n">
-        <v>2274</v>
+        <v>3468</v>
       </c>
       <c r="Q135" s="6" t="n">
-        <v>67298</v>
+        <v>102639</v>
       </c>
     </row>
     <row r="136" ht="19" customHeight="1">
@@ -9084,16 +9084,16 @@
         <v>2.3</v>
       </c>
       <c r="N136" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O136" s="6" t="n">
-        <v>1148</v>
+        <v>1751</v>
       </c>
       <c r="P136" s="6" t="n">
-        <v>2296</v>
+        <v>3502</v>
       </c>
       <c r="Q136" s="6" t="n">
-        <v>68446</v>
+        <v>104390</v>
       </c>
     </row>
     <row r="137" ht="19" customHeight="1">
@@ -9147,16 +9147,16 @@
         <v>2.3</v>
       </c>
       <c r="N137" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O137" s="6" t="n">
-        <v>1160</v>
+        <v>1769</v>
       </c>
       <c r="P137" s="6" t="n">
-        <v>2320</v>
+        <v>3538</v>
       </c>
       <c r="Q137" s="6" t="n">
-        <v>69606</v>
+        <v>106159</v>
       </c>
     </row>
     <row r="138" ht="19" customHeight="1">
@@ -9210,16 +9210,16 @@
         <v>2.3</v>
       </c>
       <c r="N138" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O138" s="6" t="n">
-        <v>1171</v>
+        <v>1786</v>
       </c>
       <c r="P138" s="6" t="n">
-        <v>2342</v>
+        <v>3572</v>
       </c>
       <c r="Q138" s="6" t="n">
-        <v>70777</v>
+        <v>107945</v>
       </c>
     </row>
     <row r="139" ht="19" customHeight="1">
@@ -9273,16 +9273,16 @@
         <v>2.3</v>
       </c>
       <c r="N139" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O139" s="6" t="n">
-        <v>1183</v>
+        <v>1804</v>
       </c>
       <c r="P139" s="6" t="n">
-        <v>2366</v>
+        <v>3608</v>
       </c>
       <c r="Q139" s="6" t="n">
-        <v>71960</v>
+        <v>109749</v>
       </c>
     </row>
     <row r="140" ht="19" customHeight="1">
@@ -9336,16 +9336,16 @@
         <v>2.3</v>
       </c>
       <c r="N140" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O140" s="6" t="n">
-        <v>1194</v>
+        <v>1822</v>
       </c>
       <c r="P140" s="6" t="n">
-        <v>2388</v>
+        <v>3644</v>
       </c>
       <c r="Q140" s="6" t="n">
-        <v>73154</v>
+        <v>111571</v>
       </c>
     </row>
     <row r="141" ht="19" customHeight="1">
@@ -9399,16 +9399,16 @@
         <v>2.3</v>
       </c>
       <c r="N141" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O141" s="6" t="n">
-        <v>1206</v>
+        <v>1839</v>
       </c>
       <c r="P141" s="6" t="n">
-        <v>2412</v>
+        <v>3678</v>
       </c>
       <c r="Q141" s="6" t="n">
-        <v>74360</v>
+        <v>113410</v>
       </c>
     </row>
     <row r="142" ht="19" customHeight="1">
@@ -9462,16 +9462,16 @@
         <v>2.3</v>
       </c>
       <c r="N142" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O142" s="6" t="n">
-        <v>1217</v>
+        <v>1857</v>
       </c>
       <c r="P142" s="6" t="n">
-        <v>2434</v>
+        <v>3714</v>
       </c>
       <c r="Q142" s="6" t="n">
-        <v>75577</v>
+        <v>115267</v>
       </c>
     </row>
     <row r="143" ht="19" customHeight="1">
@@ -9525,16 +9525,16 @@
         <v>2.3</v>
       </c>
       <c r="N143" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O143" s="6" t="n">
-        <v>1229</v>
+        <v>1874</v>
       </c>
       <c r="P143" s="6" t="n">
-        <v>2458</v>
+        <v>3748</v>
       </c>
       <c r="Q143" s="6" t="n">
-        <v>76806</v>
+        <v>117141</v>
       </c>
     </row>
     <row r="144" ht="19" customHeight="1">
@@ -9588,16 +9588,16 @@
         <v>2.3</v>
       </c>
       <c r="N144" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O144" s="6" t="n">
-        <v>1241</v>
+        <v>1892</v>
       </c>
       <c r="P144" s="6" t="n">
-        <v>2482</v>
+        <v>3784</v>
       </c>
       <c r="Q144" s="6" t="n">
-        <v>78047</v>
+        <v>119033</v>
       </c>
     </row>
     <row r="145" ht="19" customHeight="1">
@@ -9651,16 +9651,16 @@
         <v>2.3</v>
       </c>
       <c r="N145" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O145" s="6" t="n">
-        <v>1252</v>
+        <v>1910</v>
       </c>
       <c r="P145" s="6" t="n">
-        <v>2504</v>
+        <v>3820</v>
       </c>
       <c r="Q145" s="6" t="n">
-        <v>79299</v>
+        <v>120943</v>
       </c>
     </row>
     <row r="146" ht="19" customHeight="1">
@@ -9714,16 +9714,16 @@
         <v>2.3</v>
       </c>
       <c r="N146" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O146" s="6" t="n">
-        <v>1264</v>
+        <v>1927</v>
       </c>
       <c r="P146" s="6" t="n">
-        <v>2528</v>
+        <v>3854</v>
       </c>
       <c r="Q146" s="6" t="n">
-        <v>80563</v>
+        <v>122870</v>
       </c>
     </row>
     <row r="147" ht="19" customHeight="1">
@@ -9777,16 +9777,16 @@
         <v>2.3</v>
       </c>
       <c r="N147" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O147" s="6" t="n">
-        <v>1275</v>
+        <v>1945</v>
       </c>
       <c r="P147" s="6" t="n">
-        <v>2550</v>
+        <v>3890</v>
       </c>
       <c r="Q147" s="6" t="n">
-        <v>81838</v>
+        <v>124815</v>
       </c>
     </row>
     <row r="148" ht="19" customHeight="1">
@@ -9840,16 +9840,16 @@
         <v>2.3</v>
       </c>
       <c r="N148" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O148" s="6" t="n">
-        <v>1287</v>
+        <v>1962</v>
       </c>
       <c r="P148" s="6" t="n">
-        <v>2574</v>
+        <v>3924</v>
       </c>
       <c r="Q148" s="6" t="n">
-        <v>83125</v>
+        <v>126777</v>
       </c>
     </row>
     <row r="149" ht="19" customHeight="1">
@@ -9903,16 +9903,16 @@
         <v>2.3</v>
       </c>
       <c r="N149" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O149" s="6" t="n">
-        <v>1298</v>
+        <v>1980</v>
       </c>
       <c r="P149" s="6" t="n">
-        <v>2596</v>
+        <v>3960</v>
       </c>
       <c r="Q149" s="6" t="n">
-        <v>84423</v>
+        <v>128757</v>
       </c>
     </row>
     <row r="150" ht="19" customHeight="1">
@@ -9966,16 +9966,16 @@
         <v>2.3</v>
       </c>
       <c r="N150" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O150" s="6" t="n">
-        <v>1310</v>
+        <v>1998</v>
       </c>
       <c r="P150" s="6" t="n">
-        <v>2620</v>
+        <v>3996</v>
       </c>
       <c r="Q150" s="6" t="n">
-        <v>85733</v>
+        <v>130755</v>
       </c>
     </row>
     <row r="151" ht="19" customHeight="1">
@@ -10029,16 +10029,16 @@
         <v>2.3</v>
       </c>
       <c r="N151" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O151" s="6" t="n">
-        <v>1321</v>
+        <v>2015</v>
       </c>
       <c r="P151" s="6" t="n">
-        <v>2642</v>
+        <v>4030</v>
       </c>
       <c r="Q151" s="6" t="n">
-        <v>87054</v>
+        <v>132770</v>
       </c>
     </row>
   </sheetData>
